--- a/assessment_forms/030_icu_skills_assessment--assessment_forms.xlsx
+++ b/assessment_forms/030_icu_skills_assessment--assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,17 +515,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>icu_skills_assessment_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>introduction</t>
+          <t>Basic Life Support</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -543,12 +543,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>basic_life_support</t>
+          <t>icu_skills_assessment_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>basic life support</t>
+          <t>Airway Management</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>basic_life_support_1</t>
+          <t>icu_skills_assessment_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>airway</t>
+          <t>Medical Complications Identification</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>airway_2</t>
+          <t>icu_skills_assessment_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>airway</t>
+          <t>Cardiac Care</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>airway_3</t>
+          <t>icu_skills_assessment_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>airway</t>
+          <t>Respiratory Care</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>airway_4</t>
+          <t>icu_skills_assessment_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>airway</t>
+          <t>Neurological Care</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>medical_complications</t>
+          <t>icu_skills_assessment_7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>medical complications</t>
+          <t>Cardiovascular Care</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>cardiac</t>
+          <t>icu_skills_assessment_8</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cardiac</t>
+          <t>Trauma Care</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>respiratory</t>
+          <t>icu_skills_assessment_9</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>respiratory</t>
+          <t>General Principles of Care</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>neurological</t>
+          <t>icu_skills_assessment_10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>neurological</t>
+          <t>Prioritization and Management of Care</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>cardiovascular</t>
+          <t>icu_skills_assessment_11</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cardiovascular</t>
+          <t>Airway Care</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_complications_2</t>
+          <t>icu_skills_assessment_12</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>medical complications 2</t>
+          <t>Medication Management</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>trauma</t>
+          <t>icu_skills_assessment_13</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>trauma</t>
+          <t>Patient Safety</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>general_principles</t>
+          <t>icu_skills_assessment_14</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>general principles</t>
+          <t>Pain Management</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,16 +842,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>trauma_2</t>
+          <t>icu_skills_assessment_15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>trauma</t>
+          <t>Sedation</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>select_multiple</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_16</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Error Identification and Management</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,12 +891,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -896,476 +919,799 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>basic_life_support_choices</t>
+          <t>icu_skills_assessment_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>cpr</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>CPR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>basic_life_support_choices</t>
+          <t>icu_skills_assessment_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>intubation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Intubation</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>basic_life_support_1_choices</t>
+          <t>icu_skills_assessment_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ventilation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ventilation</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>basic_life_support_1_choices</t>
+          <t>icu_skills_assessment_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Others</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>airway_2_choices</t>
+          <t>icu_skills_assessment_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>intubation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Intubation</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>airway_2_choices</t>
+          <t>icu_skills_assessment_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>ventilation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Ventilation</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>airway_3_choices</t>
+          <t>icu_skills_assessment_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>oxygenation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Oxygenation</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>airway_3_choices</t>
+          <t>icu_skills_assessment_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hypertension</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hypertension</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>airway_4_choices</t>
+          <t>icu_skills_assessment_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>hypoglycemia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Hypoglycemia</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>airway_4_choices</t>
+          <t>icu_skills_assessment_3_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>hypoxemia</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Hypoxemia</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medical_complications_choices</t>
+          <t>icu_skills_assessment_3_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>others</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>others</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medical_complications_choices</t>
+          <t>icu_skills_assessment_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monitoring</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>cardiac_choices</t>
+          <t>icu_skills_assessment_4_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Interventions</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>cardiac_choices</t>
+          <t>icu_skills_assessment_4_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medecine</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medecine</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>respiratory_choices</t>
+          <t>icu_skills_assessment_5_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>ventilation</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Ventilation</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>respiratory_choices</t>
+          <t>icu_skills_assessment_5_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>oxygenation</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Oxygenation</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>neurological_choices</t>
+          <t>icu_skills_assessment_5_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>pneumonia</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Pneumonia</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>neurological_choices</t>
+          <t>icu_skills_assessment_7_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monitoring</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monitoring</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cardiovascular_choices</t>
+          <t>icu_skills_assessment_7_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>interventions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Interventions</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>cardiovascular_choices</t>
+          <t>icu_skills_assessment_7_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>medecine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Medecine</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>medical_complications_2_choices</t>
+          <t>icu_skills_assessment_8_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>triage</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Triage</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>medical_complications_2_choices</t>
+          <t>icu_skills_assessment_8_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>resuscitation</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Resuscitation</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>trauma_choices</t>
+          <t>icu_skills_assessment_8_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>surgery</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Surgery</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>trauma_choices</t>
+          <t>icu_skills_assessment_9_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>general_principles_choices</t>
+          <t>icu_skills_assessment_9_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>teamwork</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Teamwork</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>general_principles_choices</t>
+          <t>icu_skills_assessment_9_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>decision_making</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Decision Making</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>trauma_2_choices</t>
+          <t>icu_skills_assessment_10_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>assess</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Assess</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>trauma_2_choices</t>
+          <t>icu_skills_assessment_10_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>plan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_10_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>intervention</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Intervention</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_11_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>intubation</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Intubation</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_11_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ventilation</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ventilation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_11_choices</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>oxygenation</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Oxygenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_12_choices</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>administer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Administer</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_12_choices</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_12_choices</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>titrate</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Titrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_13_choices</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>fall_prevention</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Fall Prevention</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_13_choices</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>ventilation</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ventilation</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_13_choices</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>oxygenation</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Oxygenation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_14_choices</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>administer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Administer</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_14_choices</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>titrate</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Titrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_14_choices</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_15_choices</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>administer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Administer</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_15_choices</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>monitor</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_15_choices</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>titrate</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Titrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_16_choices</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>recognize</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Recognize</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_16_choices</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>report</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Report</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>icu_skills_assessment_16_choices</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>correct</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Correct</t>
         </is>
       </c>
     </row>
